--- a/data/skills.xlsx
+++ b/data/skills.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Acrobatics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Athletics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Diplomacy" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Guile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Intimidation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Stealth" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acrobatics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Athletics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diplomacy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intimidation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stealth" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -698,21 +698,21 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You are Trained in this skill: add the Constellation's rank to its checks. Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tumbling Retreat ◆</t>
+          <t>Tumbling Retreat ❶</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -720,21 +720,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Acrobatics Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Step 6 feet instead of 3. You still cannot Step in Difficult Terrain or Greater Difficult Terrain.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Step your full Speed away from your foes. You still cannot Step in Difficult Terrain or Greater Difficult Terrain.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -747,26 +747,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Acrobatics Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+2 circumstance bonus to Escape.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>+2 Situation bonus to Escape.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Kip Up ◆</t>
+          <t>Kip Up ❶</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -774,21 +774,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Acrobatics Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Stand up. This movement doesn't trigger reactions.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>Stand up. This movement doesn't trigger Reactions.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -801,21 +801,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Kip Up</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>When you Stand, you may Step as part of the same action.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -828,21 +828,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Acrobatics Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>When you successfully Tumble Through, the foe whose space you passed through is Wrong-Footed against the next attack you make before the end of your current turn.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>When you successfully Tumble Through, the foe whose space you passed through is Wrong-Footed against the next attack you make before the end of your next Opportunity.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -855,21 +855,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Acrobatics Training</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>When you Stride and move half your Speed or less, that movement does not trigger reactions. You can use Mobility when Climbing, Flying, or Swimming instead of Striding if you have the corresponding movement type.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t>When you Move half your Speed or less, that movement does not trigger Intercepts or other Reactions. You can use Mobility when Climbing, Flying, or Swimming instead of Moving if you have the corresponding movement type.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -959,21 +959,21 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You are Trained in this skill: add the Constellation's rank to its checks. Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Bull Rush ◆◆</t>
+          <t>Bull Rush ❷</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -981,22 +981,22 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Athletics Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Stride, then Shove.
-Add 3 feet to the push for every 10 feet you moved first.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Move, then Shove.
+Add 1 foot to the push for every 2 feet you moved first.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1009,21 +1009,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Athletics Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A creature you have Grabbed takes a −2 circumstance penalty to Escape.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>A creature you have Grabbed takes a −2 Situation penalty to Escape.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1036,21 +1036,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Athletics Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Grapple, Shove, and Trip creatures up to two sizes larger than you.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1140,21 +1140,21 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You are Trained in this skill: add the Constellation's rank to its checks. Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Rally ◆</t>
+          <t>Rally ❶</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1162,28 +1162,53 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Diplomacy Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>You gain the Rally ◆ action:
-Rally ◆  Auditory, Emotion, Mental
-Roll Diplomacy against a Threshold of 14 + your level. On a success, one ally within 30 feet who can hear you gains a +1 circumstance bonus to their next Defense roll before the start of your next turn. On a critical success, +2, and they can Recenter ◆ as a free action.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">You gain the Rally ❶ action:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Rally ❶</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Auditory, Emotion, Mental</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Roll Diplomacy against a Threshold of 14. On a success, one ally within 30 feet who can hear you gains a +1 Situation bonus to their next Defense roll before your next Opportunity. On a critical success, +2, and they can Recenter ❶ as a free action.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Talk Them Down ◆</t>
+          <t>Talk Them Down ❶</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1191,23 +1216,48 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Diplomacy Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>You gain the Talk Them Down ◆ action:
-Talk Them Down ◆  Auditory, Concentrate, Emotion, Mental
-Roll Diplomacy against the target's Guard. On a success, it takes a −2 circumstance penalty to Attacks against you until the end of your next turn; on a critical success, until the end of the encounter. On a critical failure it gains a +1 circumstance bonus to Attacks against you.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">You gain the Talk Them Down ❶ action:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Talk Them Down ❶</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Auditory, Concentrate, Emotion, Mental</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Roll Diplomacy against the target's Guard. On a success, it takes a -2 Situation penalty to Attacks against you until the end of the next round; on a critical success, until the end of the encounter. On a critical failure it gains a +1 Situation bonus to Attacks against you.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1220,26 +1270,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Diplomacy Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>When you Aid an ally, the bonus is +2 instead of +1, and +3 on a critical success.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Command the Field ◆◆</t>
+          <t>Command the Field ❷</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1247,23 +1297,48 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Diplomacy Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>You gain the Command the Field ◆◆ action:
-Command the Field ◆◆  Auditory, Concentrate, Emotion, Mental
-Roll Diplomacy against a Threshold of 14 + your level. On a success, two allies who can hear you may each Step as a free action. On a critical success, they may each Stride half their Speed instead.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">You gain the Command the Field ❷ action:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Command the Field ❷</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Auditory, Concentrate, Emotion, Mental</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Roll Diplomacy against a Threshold of 14. On a Success, two allies who can hear you may each Step ⓿. On a critical success, they may each Move half their Speed instead.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1353,21 +1428,21 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You are Trained in this skill: add the Constellation's rank to its checks. Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Feinting Step ◆</t>
+          <t>Feinting Step ❶</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1375,21 +1450,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Guile Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Feint, then Step.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1402,21 +1477,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Guile Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>When you critically succeed at a Feint, the target is Off-Guard to everyone, not just you, until the end of your next turn.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>When you critically succeed at a Feint, the target is off-guard to everyone, not just you, until the end of the next round.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1429,23 +1504,47 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Guile Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>On a successful Feint, you can use the following success and critical success effects instead of any other effects that would occur when you Feint.
-Critical Success The target takes a −2 circumstance penalty to all attack rolls against you before the end of its next turn.
-Success The target takes a −2 circumstance penalty to its next attack roll against you before the end of its next turn.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">On a successful Feint, you can use the following success and critical success effects instead of any other effects that would occur when you Feint.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Critical Success</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The target takes a -2 Situation penalty to all attack rolls against you before the end of the next round.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Success</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The target takes a -2 Situation penalty to its next attack roll against you before the end of the next round.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1458,21 +1557,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Guile Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>While a creature is Off-Guard or Wrong-Footed by your Feints, it also takes a −2 circumstance penalty to Awareness and Agility checks and Thresholds.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>While a creature is Off-Guard or Wrong-Footed by your Feints, it also takes a -2 Situation penalty to Awareness and Agility checks and Thresholds.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1562,21 +1661,21 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You are Trained in this skill: add the Constellation's rank to its checks. Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Battle Cry ◇</t>
+          <t>Battle Cry ⓿↺</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1584,22 +1683,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Intimidation Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Trigger You are about to roll Initiative.
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are about to roll Initiative.
 Demoralize every enemy within 15 feet with a single roll, compared separately against each one's Guard.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1612,21 +1721,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Intimidation Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>When you drop a creature, you may Demoralize one enemy who saw it fall as a free action.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>When you drop a creature, you may Demoralize ⓿ one enemy who saw it fall.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1639,21 +1748,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Intimidation Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A creature you have Demoralized this encounter takes a −1 circumstance penalty to attacks against you for the rest of it.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>A creature you have Demoralized this encounter takes a −1 Situation penalty to attacks against you for the rest of it.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1666,21 +1775,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Intimidation Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Whenever your Strike is a critical hit and deals damage, the target is Frightened 1.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1770,16 +1879,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You are Trained in this skill: add the Constellation's rank to its checks. Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1792,26 +1901,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Stealth Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>When you Hit a creature that is Off-Guard or Wrong-Footed to you, you choose which Zone the blow lands on.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Lost in the Noise ↺</t>
+          <t>Lost in the Noise ❶↺</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1819,22 +1928,43 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Stealth Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Trigger An attack against you Misses.
-Effect If you have cover or concealment, Hide as part of this reaction.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> An attack against you Misses.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Effect</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> If you have cover or concealment, Hide as part of this Reaction.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,26 +1977,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Stealth Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>The first time each encounter that you Strike a creature that is unaware of you, a Graze becomes a Hit.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Underhanded Assault ◆◆</t>
+          <t>Underhanded Assault ❷</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1874,21 +2004,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Stealth Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>You Sneak up to a foe adjacent to one of your allies. You can roll against the foe you're Sneaking up on, even if it's currently observing you, as though you were hidden. You take a −2 penalty on your Stealth check. If your Stealth check against the chosen foe succeeds, you can make a melee Strike against that foe at the end of your Sneak, and they are Wrong-Footed against that Strike.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>You Sneak up to a foe adjacent to one of your allies. You can roll against the foe you're Sneaking up on, even if it's currently observing you, as though you were hidden. You take a -2 penalty on your Stealth check. If your Stealth check against the chosen foe succeeds, you can make a melee Strike against that foe at the end of your Sneak, and they are Wrong-Footed against that Strike.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/skills.xlsx
+++ b/data/skills.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,14 +15,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stealth" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,9 +31,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E5F6B"/>
+        <fgColor rgb="FF0E5F6B"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,7 +77,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -472,7 +477,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Acrobatics</t>
@@ -493,9 +498,9 @@
           <t>Crit succeed or crit fail on any roll with consequences, directly related to a talent in this constellation.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Athletics</t>
@@ -516,9 +521,9 @@
           <t>Crit succeed or crit fail on any roll with consequences, directly related to a talent in this constellation.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Diplomacy</t>
@@ -539,9 +544,9 @@
           <t>Crit succeed or crit fail on any roll with consequences, directly related to a talent in this constellation.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Guile</t>
@@ -562,9 +567,9 @@
           <t>Crit succeed or crit fail on any roll with consequences, directly related to a talent in this constellation.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Intimidation</t>
@@ -585,9 +590,9 @@
           <t>Crit succeed or crit fail on any roll with consequences, directly related to a talent in this constellation.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Stealth</t>
@@ -608,7 +613,7 @@
           <t>Crit succeed or crit fail on any roll with consequences, directly related to a talent in this constellation.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -621,14 +626,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -681,6 +684,11 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -708,8 +716,13 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
-    </row>
-    <row r="3">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Tumbling Retreat ❶</t>
@@ -735,6 +748,11 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -762,6 +780,11 @@
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -789,6 +812,11 @@
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -816,8 +844,13 @@
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
-    </row>
-    <row r="7">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Tumble Behind</t>
@@ -843,8 +876,13 @@
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
-    </row>
-    <row r="8">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Mobility</t>
@@ -870,6 +908,11 @@
       </c>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -882,14 +925,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -942,6 +983,11 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -969,8 +1015,13 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
-    </row>
-    <row r="3">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Bull Rush ❷</t>
@@ -997,6 +1048,11 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1024,6 +1080,11 @@
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1051,6 +1112,11 @@
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1063,14 +1129,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1123,6 +1187,11 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1220,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Rally ❶</t>
@@ -1178,23 +1247,10 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
             </rPr>
-            <t>Rally ❶</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Auditory, Emotion, Mental</t>
+            <t>Rally ❶
+Auditory, Emotion, Mental</t>
           </r>
           <r>
             <t xml:space="preserve">
@@ -1205,7 +1261,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Talk Them Down ❶</t>
@@ -1232,23 +1288,10 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
             </rPr>
-            <t>Talk Them Down ❶</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Auditory, Concentrate, Emotion, Mental</t>
+            <t>Talk Them Down ❶
+Auditory, Concentrate, Emotion, Mental</t>
           </r>
           <r>
             <t xml:space="preserve">
@@ -1286,7 +1329,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Command the Field ❷</t>
@@ -1313,23 +1356,10 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
             </rPr>
-            <t>Command the Field ❷</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Auditory, Concentrate, Emotion, Mental</t>
+            <t>Command the Field ❷
+Auditory, Concentrate, Emotion, Mental</t>
           </r>
           <r>
             <t xml:space="preserve">
@@ -1351,14 +1381,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1411,6 +1439,11 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1466,7 +1499,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Sell the Feint</t>
@@ -1493,7 +1526,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Overextending Feint</t>
@@ -1527,6 +1560,13 @@
             <t>Critical Success</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> The target takes a -2 Situation penalty to all attack rolls against you before the end of the next round.
 </t>
           </r>
@@ -1539,6 +1579,13 @@
             <t>Success</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> The target takes a -2 Situation penalty to its next attack roll against you before the end of the next round.</t>
           </r>
         </is>
@@ -1546,7 +1593,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Distracting Feint</t>
@@ -1584,14 +1631,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1644,6 +1689,11 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1672,7 +1722,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Battle Cry ⓿↺</t>
@@ -1702,6 +1752,13 @@
             <t>Trigger</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You are about to roll Initiative.
 Demoralize every enemy within 15 feet with a single roll, compared separately against each one's Guard.</t>
           </r>
@@ -1737,7 +1794,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Unnerving</t>
@@ -1802,14 +1859,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1862,6 +1917,11 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1890,7 +1950,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Knife in the Dark</t>
@@ -1917,7 +1977,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Lost in the Noise ❶↺</t>
@@ -1947,6 +2007,13 @@
             <t>Trigger</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> An attack against you Misses.
 </t>
           </r>
@@ -1959,6 +2026,13 @@
             <t>Effect</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> If you have cover or concealment, Hide as part of this Reaction.</t>
           </r>
         </is>
@@ -1993,7 +2067,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Underhanded Assault ❷</t>

--- a/data/skills.xlsx
+++ b/data/skills.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -687,6 +689,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -925,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -935,6 +942,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -986,6 +995,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1153,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1190,6 +1206,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1260,6 +1281,11 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>30 ft allies</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1381,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1391,6 +1417,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1442,6 +1470,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1641,6 +1674,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1692,6 +1727,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1766,6 +1806,11 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>15 ft enemies</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1859,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1869,6 +1914,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1920,6 +1967,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
